--- a/processed_ruby_restored_xlsx/sc227_瑠璃９：かけおち.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc227_瑠璃９：かけおち.ss.xlsx
@@ -609,8 +609,9 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>「I've prepared the long-weekend homework properly, you
-know~？ Don't slack off — make sure you do it right！」</t>
+          <t>「I've prepared the long-weekend homework properly,
+you know~？ Don't slack off — make sure you do it
+right！」</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -656,8 +657,8 @@
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>I get a bit overexcited, which is my only flaw, but
-since it's what the teacher says, I'll feel down about
-it but I won't complain.</t>
+since it's what the teacher says, I'll feel down
+about it but I won't complain.</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -889,8 +890,8 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, being Nono-chan, quietly voices her wish to
-her.</t>
+          <t>Nono-chan, being Nono-chan, quietly voices her wish
+to her.</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1089,8 +1090,8 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>...Then, having stayed quiet until now, Rurichiyo-chan
-slowly raised her hand.</t>
+          <t>...Then, having stayed quiet until now,
+Rurichiyo-chan slowly raised her hand.</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1226,8 +1227,8 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>「Yes, since I didn't go home during summer break, I've
-been told to come back once...」</t>
+          <t>「Yes, since I didn't go home during summer break,
+I've been told to come back once...」</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1394,8 +1395,8 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Listening to everyone speak in turn, I remembered what
-had happened right after summer break.</t>
+          <t>Listening to everyone speak in turn, I remembered
+what had happened right after summer break.</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1426,9 +1427,9 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>In fact, there had been no interference from the Honke
-since then, so this order for Rurichiyo-chan to go
-home surprised me too.</t>
+          <t>In fact, there had been no interference from the
+Honke since then, so this order for Rurichiyo-chan to
+go home surprised me too.</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1886,8 +1887,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>「Because Rin kept pretending to grab it over and over,
-geez！ Ugh！」</t>
+          <t>「Because Rin kept pretending to grab it over and
+over, geez！ Ugh！」</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2010,9 +2011,9 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan was like a mother to everyone, so she’d
-naturally ended up being the one who kept things in
-check….</t>
+          <t>Rurichiyo-chan was like a mother to everyone, so
+she’d naturally ended up being the one who kept
+things in check….</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2406,8 +2407,8 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Both of them glare at me, determined to see everything
-in black and white.</t>
+          <t>Both of them glare at me, determined to see
+everything in black and white.</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3260,9 +3261,9 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Peeking out from behind the living room door, Rin-chan
-let out a cautious voice as if she'd seen something
-strange.</t>
+          <t>Peeking out from behind the living room door,
+Rin-chan let out a cautious voice as if she'd seen
+something strange.</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3762,8 +3763,8 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>「I don't know, but…I've never seen Rurichiyo-chan like
-that before…」</t>
+          <t>「I don't know, but…I've never seen Rurichiyo-chan
+like that before…」</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4052,9 +4053,9 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>She came into the room without even knocking properly,
-and Rurichiyo-chan was sitting on a chair, swinging
-her legs.</t>
+          <t>She came into the room without even knocking
+properly, and Rurichiyo-chan was sitting on a chair,
+swinging her legs.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4144,8 +4145,8 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>It was rare to see Rurichiyo-chan take such a stubborn
-attitude.</t>
+          <t>It was rare to see Rurichiyo-chan take such a
+stubborn attitude.</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4476,8 +4477,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>...That's what I was thinking in my head, but my mouth
-stayed open and no words came out.</t>
+          <t>...That's what I was thinking in my head, but my
+mouth stayed open and no words came out.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -5060,8 +5061,8 @@
       <c r="B301" s="1" t="inlineStr">
         <is>
           <t>…To be honest, even I thought it was reckless as soon
-as I said it, and I didn't expect her to go along with
-it.</t>
+as I said it, and I didn't expect her to go along
+with it.</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5092,8 +5093,8 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>If I back out right now, I’ll just rile Rurichiyo-chan
-up even more.</t>
+          <t>If I back out right now, I’ll just rile
+Rurichiyo-chan up even more.</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5572,8 +5573,8 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>…Eloping is totally ridiculous to begin with, but what
-about just playing at eloping?</t>
+          <t>…Eloping is totally ridiculous to begin with, but
+what about just playing at eloping?</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5665,7 +5666,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>I wiped the sweat trickling down and let out a breath.</t>
+          <t>I wiped the sweat trickling down and let out a
+breath.</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -6166,7 +6168,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan widened her eyes and looked back at me.</t>
+          <t>Rurichiyo-chan widened her eyes and looked back at
+me.</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6561,8 +6564,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>If you picture a ryokan's tatami room, this is exactly
-what you'd imagine.</t>
+          <t>If you picture a ryokan's tatami room, this is
+exactly what you'd imagine.</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6637,8 +6640,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>Seeing Rurichiyo-chan getting excited at the tatami, I
-thought I’d like to bring Nono-chan along too.</t>
+          <t>Seeing Rurichiyo-chan getting excited at the tatami,
+I thought I’d like to bring Nono-chan along too.</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6775,8 +6778,8 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ I'm so happy we can stay in a place like this...
-but how did you manage to get a reservation？」</t>
+          <t>「Yes！ I'm so happy we can stay in a place like
+this... but how did you manage to get a reservation？」</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6806,8 +6809,8 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... well, it's the internet age now, so you can
-make same-day reservations anytime...！」</t>
+          <t>「Y-yeah... well, it's the internet age now, so you
+can make same-day reservations anytime...！」</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6991,8 +6994,8 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>If I'm thinking about the kid I left at the dorm, this
-runaway-game should be over within the holiday.</t>
+          <t>If I'm thinking about the kid I left at the dorm,
+this runaway-game should be over within the holiday.</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7023,7 +7026,8 @@
       <c r="B428" s="1" t="inlineStr">
         <is>
           <t>「This ryokan even has a family bath you can go into
-alone together... of course, I've made a reservation.」</t>
+alone together... of course, I've made a
+reservation.」</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7831,8 +7835,9 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>When someone pours hot water over my back, even though
-it's not really ticklish, I end up feeling ticklish.</t>
+          <t>When someone pours hot water over my back, even
+though it's not really ticklish, I end up feeling
+ticklish.</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -7909,9 +7914,9 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>The ferry ride was pretty long, and then we took a bus
-along unfamiliar roads, so I was probably mentally
-worn out.</t>
+          <t>The ferry ride was pretty long, and then we took a
+bus along unfamiliar roads, so I was probably
+mentally worn out.</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -7926,8 +7931,8 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>Last night took extra work to get ready too, so that’s
-probably catching up with me...</t>
+          <t>Last night took extra work to get ready too, so
+that’s probably catching up with me...</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -8540,7 +8545,8 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>Thinking that makes me want to cling to her even more.</t>
+          <t>Thinking that makes me want to cling to her even
+more.</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8677,8 +8683,8 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>At a loss for words, I nodded, and Rurichiyo-chan gave
-a little twitch in response.</t>
+          <t>At a loss for words, I nodded, and Rurichiyo-chan
+gave a little twitch in response.</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -9104,7 +9110,8 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan smiled as if to say it can't be helped.</t>
+          <t>Rurichiyo-chan smiled as if to say it can't be
+helped.</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -9241,8 +9248,8 @@
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
-          <t>Seen through again, I hid my embarrassment by pressing
-my face into her thigh.</t>
+          <t>Seen through again, I hid my embarrassment by
+pressing my face into her thigh.</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9794,8 +9801,8 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>I whined and made up a flimsy excuse while bringing my
-mouth up to Rurichiyo-chan's between-her-legs.</t>
+          <t>I whined and made up a flimsy excuse while bringing
+my mouth up to Rurichiyo-chan's between-her-legs.</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -10221,8 +10228,8 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>There's a bit of resistance, but even that gets me all
-worked up...</t>
+          <t>There's a bit of resistance, but even that gets me
+all worked up...</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10343,8 +10350,8 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>「Nn...ahh, uncle...sir...！ But... I still can't... not
-here... nnn！」</t>
+          <t>「Nn...ahh, uncle...sir...！ But... I still can't...
+not here... nnn！」</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10389,8 +10396,8 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>I stuck my tongue out and chewed over Rurichiyo-chan's
-words in my head.</t>
+          <t>I stuck my tongue out and chewed over
+Rurichiyo-chan's words in my head.</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10406,8 +10413,8 @@
       <c r="B649" s="1" t="inlineStr">
         <is>
           <t>Ahh... Rurichiyo-chan, you're getting all
-self-conscious about the place—so that's what's making
-you more sensitive？</t>
+self-conscious about the place—so that's what's
+making you more sensitive？</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10792,8 +10799,8 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>As expected, acting clingy and saying it is incredibly
-effective.</t>
+          <t>As expected, acting clingy and saying it is
+incredibly effective.</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10808,8 +10815,8 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>I feel a little guilty, like I’m deceiving you… but no
-— screw it, I’ll just go all in on leaning on you！</t>
+          <t>I feel a little guilty, like I’m deceiving you… but
+no — screw it, I’ll just go all in on leaning on you！</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -11130,8 +11137,8 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>When I heard a sigh that sounded so pleasurable, I got
-excited and felt happy too...！</t>
+          <t>When I heard a sigh that sounded so pleasurable, I
+got excited and felt happy too...！</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -11254,8 +11261,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ahfu, fuu... yaa, it’s so amazing... between my
-legs... I feel like I’m going to melt...」</t>
+          <t>「Ah... ahfu, fuu... yaa, it’s so amazing... between
+my legs... I feel like I’m going to melt...」</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11500,9 +11507,9 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>Looks like the stimulation is a bit too intense, but I
-wonder if once she gets used to it she'll react like
-she did earlier...？</t>
+          <t>Looks like the stimulation is a bit too intense, but
+I wonder if once she gets used to it she'll react
+like she did earlier...？</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -11777,8 +11784,8 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>I've been shoved and came from a penis many times, but
-I'd never had my tongue used so thoroughly like
+          <t>I've been shoved and came from a penis many times,
+but I'd never had my tongue used so thoroughly like
 this...</t>
         </is>
       </c>
@@ -12086,8 +12093,9 @@
       </c>
       <c r="B758" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan imagines in an instant what's happening
-between her legs and claps both hands over her cheeks.</t>
+          <t>Rurichiyo-chan imagines in an instant what's
+happening between her legs and claps both hands over
+her cheeks.</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -12560,9 +12568,9 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>When I casually called her seductive, Rurichiyo-chan's
-face flushed bright red and her mouth started
-fluttering.</t>
+          <t>When I casually called her seductive,
+Rurichiyo-chan's face flushed bright red and her
+mouth started fluttering.</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12671,8 +12679,8 @@
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>It should be less stimulating than Kuri, but right now
-she seems to feel it more intensely.</t>
+          <t>It should be less stimulating than Kuri, but right
+now she seems to feel it more intensely.</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -12930,7 +12938,8 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>「Uwa... ah...! Th-that's... no... Oji-sama! Kuu... n!」</t>
+          <t>「Uwa... ah...! Th-that's... no... Oji-sama! Kuu...
+n!」</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13082,8 +13091,8 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>Just as her intense reaction suddenly relaxed, a spray
-spurted from between Rurichiyo's legs.</t>
+          <t>Just as her intense reaction suddenly relaxed, a
+spray spurted from between Rurichiyo's legs.</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -13560,8 +13569,8 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan puffs out her cheeks and turns her face
-away.</t>
+          <t>Rurichiyo-chan puffs out her cheeks and turns her
+face away.</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -13962,8 +13971,8 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>I press the tip of my penis against the soft flesh and
-squeeze it, but still doesn't try to put it in.</t>
+          <t>I press the tip of my penis against the soft flesh
+and squeeze it, but still doesn't try to put it in.</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -14084,8 +14093,8 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>I can't believe thoughtful Rurichiyo-chan is so turned
-on that she's just begging for a penis.</t>
+          <t>I can't believe thoughtful Rurichiyo-chan is so
+turned on that she's just begging for a penis.</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14177,8 +14186,9 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>She tightened her mouth to stifle her voice, but there
-was no doubt the muffled sound was a blissful cry.</t>
+          <t>She tightened her mouth to stifle her voice, but
+there was no doubt the muffled sound was a blissful
+cry.</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -14561,8 +14571,9 @@
       </c>
       <c r="B919" s="1" t="inlineStr">
         <is>
-          <t>Maybe because she came from cunnilingus, the sensation
-of her vaginal lining felt unbelievably good.</t>
+          <t>Maybe because she came from cunnilingus, the
+sensation of her vaginal lining felt unbelievably
+good.</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -14702,8 +14713,9 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Y-yes. It feels better when you go all the way
-deep into my stomach... nngh！ I-I'm feeling it...！」</t>
+          <t>「Mmm... Y-yes. It feels better when you go all the
+way deep into my stomach... nngh！ I-I'm feeling
+it...！」</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -14857,8 +14869,8 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>I'm feeling too much myself, and only trite words come
-out.</t>
+          <t>I'm feeling too much myself, and only trite words
+come out.</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -14918,8 +14930,8 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>「Inside Rurichiyo-chan… it’s so hot and so slippery… I
-can’t think about anything anymore…」</t>
+          <t>「Inside Rurichiyo-chan… it’s so hot and so slippery…
+I can’t think about anything anymore…」</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -14964,8 +14976,8 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan moans embarrassedly, but keeps grinding
-her butt against me.</t>
+          <t>Rurichiyo-chan moans embarrassedly, but keeps
+grinding her butt against me.</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -14980,7 +14992,8 @@
       </c>
       <c r="B946" s="1" t="inlineStr">
         <is>
-          <t>I'm embarrassed, but I can't stop how good it feels...</t>
+          <t>I'm embarrassed, but I can't stop how good it
+feels...</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -15225,8 +15238,8 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>And wetness leaks again from her womb, steadily making
-the inside of her vagina grow hot...</t>
+          <t>And wetness leaks again from her womb, steadily
+making the inside of her vagina grow hot...</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -15779,7 +15792,8 @@
       </c>
       <c r="B998" s="1" t="inlineStr">
         <is>
-          <t>She'd probably made an embarrassing image in her head.</t>
+          <t>She'd probably made an embarrassing image in her
+head.</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -16437,8 +16451,8 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>Even though I thought I was teasing Rurichiyo-chan, it
-was obvious I was the one being spoiled.</t>
+          <t>Even though I thought I was teasing Rurichiyo-chan,
+it was obvious I was the one being spoiled.</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16468,8 +16482,8 @@
       </c>
       <c r="B1043" s="1" t="inlineStr">
         <is>
-          <t>「Like you always do… you can, you know, keep going and
-make it all juicy and squelchy…？」</t>
+          <t>「Like you always do… you can, you know, keep going
+and make it all juicy and squelchy…？」</t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -16653,8 +16667,8 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan glances back at me while trying to look
-righteous.</t>
+          <t>Rurichiyo-chan glances back at me while trying to
+look righteous.</t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -17220,7 +17234,8 @@
       <c r="B1092" s="1" t="inlineStr">
         <is>
           <t>Feeling the folds of her vaginal walls stir, savoring
-each thrust as if to really taste every single one...！</t>
+each thrust as if to really taste every single
+one...！</t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -17360,8 +17375,8 @@
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>…I can tell we’re both feeling good, and thinking that
-way sent my sensitivity through the roof.</t>
+          <t>…I can tell we’re both feeling good, and thinking
+that way sent my sensitivity through the roof.</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -17377,7 +17392,8 @@
       <c r="B1102" s="1" t="inlineStr">
         <is>
           <t>It kept rising and rising—I felt like my head might
-fly off, but I grit my teeth and kept moving my hips…！</t>
+fly off, but I grit my teeth and kept moving my
+hips…！</t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -18160,8 +18176,8 @@
       <c r="B1153" s="1" t="inlineStr">
         <is>
           <t>The throbbing of my penis and the tightening of her
-pussy were perfectly in sync, to the point I felt like
-even our mucous membranes had become one.</t>
+pussy were perfectly in sync, to the point I felt
+like even our mucous membranes had become one.</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -18729,9 +18745,9 @@
       </c>
       <c r="B1190" s="1" t="inlineStr">
         <is>
-          <t>She’s probably still riding the afterglow of her peak,
-but after being cum on, it even looks like she came
-again…！</t>
+          <t>She’s probably still riding the afterglow of her
+peak, but after being cum on, it even looks like she
+came again…！</t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -18960,7 +18976,8 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnn！ Huuuh！ Nn！！ Fwaaah... nn！ Nnhuuh... nnn...！」</t>
+          <t>「Nn！ Nnn！ Huuuh！ Nn！！ Fwaaah... nn！ Nnhuuh...
+nnn...！」</t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -18991,8 +19008,8 @@
       </c>
       <c r="B1207" s="1" t="inlineStr">
         <is>
-          <t>Her body was twitching all over, like she still wanted
-to bask in the afterglow of orgasm...</t>
+          <t>Her body was twitching all over, like she still
+wanted to bask in the afterglow of orgasm...</t>
         </is>
       </c>
       <c r="C1207" t="n">
@@ -19341,8 +19358,8 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>「Yes... I'm okay... it felt really, really good, after
-all...」</t>
+          <t>「Yes... I'm okay... it felt really, really good,
+after all...」</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -19493,9 +19510,9 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>With a graceful girl like Rurichiyo, even the sight of
-her trying to hold back looks picturesque, so it's fun
-to watch...</t>
+          <t>With a graceful girl like Rurichiyo, even the sight
+of her trying to hold back looks picturesque, so it's
+fun to watch...</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19739,8 +19756,8 @@
       <c r="B1256" s="1" t="inlineStr">
         <is>
           <t>Sitting in front would let me see Rurichiyo-chan's
-nakedness and her embarrassed face, but I deliberately
-went to the back for a little reason.</t>
+nakedness and her embarrassed face, but I
+deliberately went to the back for a little reason.</t>
         </is>
       </c>
       <c r="C1256" t="n">
@@ -20123,8 +20140,8 @@
       </c>
       <c r="B1281" s="1" t="inlineStr">
         <is>
-          <t>She’d been getting so worked up earlier that even just
-washing makes her sensitive, I guess...</t>
+          <t>She’d been getting so worked up earlier that even
+just washing makes her sensitive, I guess...</t>
         </is>
       </c>
       <c r="C1281" t="n">
@@ -20214,8 +20231,8 @@
       </c>
       <c r="B1287" s="1" t="inlineStr">
         <is>
-          <t>I hook the towel around my finger and, with a touch so
-gentle it’s almost not touching, wash between her
+          <t>I hook the towel around my finger and, with a touch
+so gentle it’s almost not touching, wash between her
 legs.</t>
         </is>
       </c>
@@ -21148,8 +21165,8 @@
       </c>
       <c r="B1348" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo and I nodded to each other and hurriedly got
-out of the bath...</t>
+          <t>Rurichiyo and I nodded to each other and hurriedly
+got out of the bath...</t>
         </is>
       </c>
       <c r="C1348" t="n">
@@ -21224,8 +21241,8 @@
       </c>
       <c r="B1353" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo and I were sitting properly on our knees, in
-front of Kikuchiyo-baa-chan who was standing
+          <t>Rurichiyo and I were sitting properly on our knees,
+in front of Kikuchiyo-baa-chan who was standing
 imposingly.</t>
         </is>
       </c>
@@ -21289,8 +21306,9 @@
       </c>
       <c r="B1357" s="1" t="inlineStr">
         <is>
-          <t>「I've mostly heard the story...！ I heard Rurichiyo ran
-out of the house, but what is the meaning of this？」</t>
+          <t>「I've mostly heard the story...！ I heard Rurichiyo
+ran out of the house, but what is the meaning of
+this？」</t>
         </is>
       </c>
       <c r="C1357" t="n">
@@ -21335,7 +21353,8 @@
       </c>
       <c r="B1360" s="1" t="inlineStr">
         <is>
-          <t>...You can't pull the wool over this old woman's eyes.</t>
+          <t>...You can't pull the wool over this old woman's
+eyes.</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -21539,8 +21558,8 @@
       </c>
       <c r="B1373" s="1" t="inlineStr">
         <is>
-          <t>「Anyway, a worthless fellow like you running off in an
-elopement — it's a hundred years too soon...！」</t>
+          <t>「Anyway, a worthless fellow like you running off in
+an elopement — it's a hundred years too soon...！」</t>
         </is>
       </c>
       <c r="C1373" t="n">
@@ -21585,8 +21604,8 @@
       </c>
       <c r="B1376" s="1" t="inlineStr">
         <is>
-          <t>Even though I haven't said anything yet, being labeled
-as having eloped makes me feel put off.</t>
+          <t>Even though I haven't said anything yet, being
+labeled as having eloped makes me feel put off.</t>
         </is>
       </c>
       <c r="C1376" t="n">
@@ -21601,9 +21620,9 @@
       </c>
       <c r="B1377" s="1" t="inlineStr">
         <is>
-          <t>...Kikuchiyo-baa-chan is as sharp as ever. She must've
-guessed it from what she knew beforehand, and she hit
-the mark.</t>
+          <t>...Kikuchiyo-baa-chan is as sharp as ever. She
+must've guessed it from what she knew beforehand, and
+she hit the mark.</t>
         </is>
       </c>
       <c r="C1377" t="n">
@@ -21772,8 +21791,8 @@
       </c>
       <c r="B1388" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo... just because you begged doesn't make you
-Hajime's get-out-of-jail card, you know？」</t>
+          <t>「Rurichiyo... just because you begged doesn't make
+you Hajime's get-out-of-jail card, you know？」</t>
         </is>
       </c>
       <c r="C1388" t="n">
@@ -22419,8 +22438,8 @@
       </c>
       <c r="B1430" s="1" t="inlineStr">
         <is>
-          <t>「Oh！ Great-great-grandma too！？ How did you get through
-it back then？」</t>
+          <t>「Oh！ Great-great-grandma too！？ How did you get
+through it back then？」</t>
         </is>
       </c>
       <c r="C1430" t="n">
@@ -22790,8 +22809,8 @@
       </c>
       <c r="B1454" s="1" t="inlineStr">
         <is>
-          <t>Oh... Kikuchiyo-baa-chan turns bright red and tries to
-hide her face in embarrassment...！</t>
+          <t>Oh... Kikuchiyo-baa-chan turns bright red and tries
+to hide her face in embarrassment...！</t>
         </is>
       </c>
       <c r="C1454" t="n">
@@ -23344,8 +23363,8 @@
       </c>
       <c r="B1490" s="1" t="inlineStr">
         <is>
-          <t>「Well, Hajime... now that it's come to this, you can't
-run away anymore, y'know？」</t>
+          <t>「Well, Hajime... now that it's come to this, you
+can't run away anymore, y'know？」</t>
         </is>
       </c>
       <c r="C1490" t="n">
@@ -23718,8 +23737,8 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>So... had Kikuchiyo-baa-chan and Rurichiyo-chan formed
-a shared understanding about me？</t>
+          <t>So... had Kikuchiyo-baa-chan and Rurichiyo-chan
+formed a shared understanding about me？</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -23938,7 +23957,8 @@
       <c r="B1528" s="1" t="inlineStr">
         <is>
           <t>And then, showing her tsundere side here,
-Kikuchiyo-baa-chan... she's definitely not ordinary...</t>
+Kikuchiyo-baa-chan... she's definitely not
+ordinary...</t>
         </is>
       </c>
       <c r="C1528" t="n">
@@ -24045,8 +24065,8 @@
       </c>
       <c r="B1535" s="1" t="inlineStr">
         <is>
-          <t>...Well then, at that, Kikuchiyo-baa-chan suddenly put
-on a face like she'd bitten and crushed a bitter
+          <t>...Well then, at that, Kikuchiyo-baa-chan suddenly
+put on a face like she'd bitten and crushed a bitter
 insect.</t>
         </is>
       </c>
@@ -24247,7 +24267,8 @@
       </c>
       <c r="B1548" s="1" t="inlineStr">
         <is>
-          <t>...How should I put it, it was downright embarrassing.</t>
+          <t>...How should I put it, it was downright
+embarrassing.</t>
         </is>
       </c>
       <c r="C1548" t="n">
@@ -24448,8 +24469,8 @@
       </c>
       <c r="B1561" s="1" t="inlineStr">
         <is>
-          <t>「Seriously, Rurichiyo-chan, you still haven't had your
-first period yet...」</t>
+          <t>「Seriously, Rurichiyo-chan, you still haven't had
+your first period yet...」</t>
         </is>
       </c>
       <c r="C1561" t="n">
@@ -24645,9 +24666,9 @@
       </c>
       <c r="B1574" s="1" t="inlineStr">
         <is>
-          <t>I thought I knew everything from taking care of her in
-the dorm, but somehow she keeps growing up without me
-noticing…</t>
+          <t>I thought I knew everything from taking care of her
+in the dorm, but somehow she keeps growing up without
+me noticing…</t>
         </is>
       </c>
       <c r="C1574" t="n">
@@ -25042,8 +25063,8 @@
       </c>
       <c r="B1600" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it, my eyes were met with Rurichiyo-chan
-lying back with her legs spread.</t>
+          <t>Before I knew it, my eyes were met with
+Rurichiyo-chan lying back with her legs spread.</t>
         </is>
       </c>
       <c r="C1600" t="n">
@@ -25260,8 +25281,8 @@
       </c>
       <c r="B1614" s="1" t="inlineStr">
         <is>
-          <t>I was overwhelmed by excitement I couldn't control and
-a kind of nervousness I'd never felt before...</t>
+          <t>I was overwhelmed by excitement I couldn't control
+and a kind of nervousness I'd never felt before...</t>
         </is>
       </c>
       <c r="C1614" t="n">
@@ -25306,8 +25327,8 @@
       </c>
       <c r="B1617" s="1" t="inlineStr">
         <is>
-          <t>But I could tell just from touching her there with the
-tip of my penis that she was so soaking wet...</t>
+          <t>But I could tell just from touching her there with
+the tip of my penis that she was so soaking wet...</t>
         </is>
       </c>
       <c r="C1617" t="n">
@@ -25322,8 +25343,8 @@
       </c>
       <c r="B1618" s="1" t="inlineStr">
         <is>
-          <t>We'd just been having sex in the bath not long ago, so
-it made sense she was wet.</t>
+          <t>We'd just been having sex in the bath not long ago,
+so it made sense she was wet.</t>
         </is>
       </c>
       <c r="C1618" t="n">
@@ -25599,8 +25620,8 @@
       </c>
       <c r="B1636" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's feeling a different kind of excitement and
-tension than usual too...</t>
+          <t>Maybe she's feeling a different kind of excitement
+and tension than usual too...</t>
         </is>
       </c>
       <c r="C1636" t="n">
@@ -25737,8 +25758,8 @@
       </c>
       <c r="B1645" s="1" t="inlineStr">
         <is>
-          <t>When Rurichiyo-chan said “No！”, I felt her between her
-legs clench around the tip.</t>
+          <t>When Rurichiyo-chan said “No！”, I felt her between
+her legs clench around the tip.</t>
         </is>
       </c>
       <c r="C1645" t="n">
@@ -25844,8 +25865,8 @@
       </c>
       <c r="B1652" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nodded happily, and the area between my
-legs softened even more to accept me….</t>
+          <t>Rurichiyo-chan nodded happily, and the area between
+my legs softened even more to accept me….</t>
         </is>
       </c>
       <c r="C1652" t="n">
@@ -26012,9 +26033,9 @@
       </c>
       <c r="B1663" s="1" t="inlineStr">
         <is>
-          <t>As the dragging, entwining insertion sensation made it
-feel like being swallowed, I shuddered, and eventually
-the penis reached all the way in.</t>
+          <t>As the dragging, entwining insertion sensation made
+it feel like being swallowed, I shuddered, and
+eventually the penis reached all the way in.</t>
         </is>
       </c>
       <c r="C1663" t="n">
@@ -26289,8 +26310,8 @@
       </c>
       <c r="B1681" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, even as pleasure was burning her whole
-body, tried to devote herself to me.</t>
+          <t>Rurichiyo-chan, even as pleasure was burning her
+whole body, tried to devote herself to me.</t>
         </is>
       </c>
       <c r="C1681" t="n">
@@ -26702,8 +26723,8 @@
       </c>
       <c r="B1708" s="1" t="inlineStr">
         <is>
-          <t>As it moves through a vagina filled with abundant love
-juices, the fluid pressed inside makes a lewd,
+          <t>As it moves through a vagina filled with abundant
+love juices, the fluid pressed inside makes a lewd,
 sloshing sound.</t>
         </is>
       </c>
@@ -27060,8 +27081,9 @@
       </c>
       <c r="B1731" s="1" t="inlineStr">
         <is>
-          <t>It was already ready when it went in, and she's plenty
-wet, so the stimulation to my penis is intense.</t>
+          <t>It was already ready when it went in, and she's
+plenty wet, so the stimulation to my penis is
+intense.</t>
         </is>
       </c>
       <c r="C1731" t="n">
@@ -27352,7 +27374,8 @@
       </c>
       <c r="B1750" s="1" t="inlineStr">
         <is>
-          <t>「Haa…haaa…！ Ah！ Ah…aaaah！ O-ji, sa-ma…ah！ Ah！ Fwaaah！」</t>
+          <t>「Haa…haaa…！ Ah！ Ah…aaaah！ O-ji, sa-ma…ah！ Ah！
+Fwaaah！」</t>
         </is>
       </c>
       <c r="C1750" t="n">
@@ -27398,8 +27421,8 @@
       </c>
       <c r="B1753" s="1" t="inlineStr">
         <is>
-          <t>She seems to have come a little, but her expression is
-so natural it's still a turn-on to watch…</t>
+          <t>She seems to have come a little, but her expression
+is so natural it's still a turn-on to watch…</t>
         </is>
       </c>
       <c r="C1753" t="n">
@@ -27429,7 +27452,8 @@
       </c>
       <c r="B1755" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah…！ Aah~！ Oji-sama…！ Oji-sama too…！ Nn, kufuu…！」</t>
+          <t>「Fwaaah…！ Aah~！ Oji-sama…！ Oji-sama too…！ Nn,
+kufuu…！」</t>
         </is>
       </c>
       <c r="C1755" t="n">
@@ -27567,10 +27591,10 @@
       </c>
       <c r="B1764" s="1" t="inlineStr">
         <is>
-          <t>A thrilling electric current ran through me, and as my
-movements slowed, my body burning with the premonition
-of climax, Rurichiyo-chan used her elbow to lift her
-upper body.</t>
+          <t>A thrilling electric current ran through me, and as
+my movements slowed, my body burning with the
+premonition of climax, Rurichiyo-chan used her elbow
+to lift her upper body.</t>
         </is>
       </c>
       <c r="C1764" t="n">
@@ -27660,8 +27684,8 @@
       </c>
       <c r="B1770" s="1" t="inlineStr">
         <is>
-          <t>When I could tell from that tiny gesture, my affection
-exploded.</t>
+          <t>When I could tell from that tiny gesture, my
+affection exploded.</t>
         </is>
       </c>
       <c r="C1770" t="n">
@@ -27829,8 +27853,8 @@
       <c r="B1781" s="1" t="inlineStr">
         <is>
           <t>But seeing Rurichiyo-chan take my semen all over her
-body only makes my affection and arousal grow stronger
-and stronger.</t>
+body only makes my affection and arousal grow
+stronger and stronger.</t>
         </is>
       </c>
       <c r="C1781" t="n">
@@ -28122,8 +28146,8 @@
       <c r="B1800" s="1" t="inlineStr">
         <is>
           <t>We both, trying to keep up the pace, started a second
-round without pulling out, but the stimulation was too
-strong for a penis that'd just cum.</t>
+round without pulling out, but the stimulation was
+too strong for a penis that'd just cum.</t>
         </is>
       </c>
       <c r="C1800" t="n">
@@ -28153,8 +28177,8 @@
       </c>
       <c r="B1802" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... nngh！  Ah— ah... aaah！  Afu— fuuu...！  Unn...
-ngh！  Ngh！」</t>
+          <t>「Nngh... nngh！  Ah— ah... aaah！  Afu— fuuu...！
+Unn... ngh！  Ngh！」</t>
         </is>
       </c>
       <c r="C1802" t="n">
@@ -28571,8 +28595,8 @@
       </c>
       <c r="B1829" s="1" t="inlineStr">
         <is>
-          <t>「A-amazing... deshu...！  Ahh... the penis is inside...
-nn！  nfuuhhh...！」</t>
+          <t>「A-amazing... deshu...！  Ahh... the penis is
+inside... nn！  nfuuhhh...！」</t>
         </is>
       </c>
       <c r="C1829" t="n">
@@ -28679,8 +28703,8 @@
       </c>
       <c r="B1836" s="1" t="inlineStr">
         <is>
-          <t>I want to feel Rurichiyo-chan with everything I've got
-too.</t>
+          <t>I want to feel Rurichiyo-chan with everything I've
+got too.</t>
         </is>
       </c>
       <c r="C1836" t="n">
@@ -28824,8 +28848,8 @@
       </c>
       <c r="B1845" s="1" t="inlineStr">
         <is>
-          <t>「Ah！？ The penis is twitching… nn… it's amazin'…！ More…
-nn！」</t>
+          <t>「Ah！？ The penis is twitching… nn… it's amazin'…！
+More… nn！」</t>
         </is>
       </c>
       <c r="C1845" t="n">
@@ -28916,8 +28940,8 @@
       </c>
       <c r="B1851" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's reaction is more bewildered than ever
-before.</t>
+          <t>Rurichiyo-chan's reaction is more bewildered than
+ever before.</t>
         </is>
       </c>
       <c r="C1851" t="n">
@@ -29056,8 +29080,8 @@
       </c>
       <c r="B1860" s="1" t="inlineStr">
         <is>
-          <t>At the moment of ejaculation I arched my back hard and
-thrust all the way in…！</t>
+          <t>At the moment of ejaculation I arched my back hard
+and thrust all the way in…！</t>
         </is>
       </c>
       <c r="C1860" t="n">
@@ -29285,8 +29309,8 @@
       </c>
       <c r="B1875" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan... do you know what I'm thinking right
-now？」</t>
+          <t>「Rurichiyo-chan... do you know what I'm thinking
+right now？」</t>
         </is>
       </c>
       <c r="C1875" t="n">
@@ -29346,8 +29370,8 @@
       </c>
       <c r="B1879" s="1" t="inlineStr">
         <is>
-          <t>And with slurred speech, she did her best to put words
-together.</t>
+          <t>And with slurred speech, she did her best to put
+words together.</t>
         </is>
       </c>
       <c r="C1879" t="n">
@@ -29607,8 +29631,8 @@
       </c>
       <c r="B1896" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan leans back and takes a deep breath with
-her chest.</t>
+          <t>Rurichiyo-chan leans back and takes a deep breath
+with her chest.</t>
         </is>
       </c>
       <c r="C1896" t="n">
@@ -29777,8 +29801,8 @@
       </c>
       <c r="B1907" s="1" t="inlineStr">
         <is>
-          <t>「Ahha... ufufu...！ Shall we keep going until we can do
-it？」</t>
+          <t>「Ahha... ufufu...！ Shall we keep going until we can
+do it？」</t>
         </is>
       </c>
       <c r="C1907" t="n">
@@ -30409,8 +30433,8 @@
       </c>
       <c r="B1948" s="1" t="inlineStr">
         <is>
-          <t>Her juices gush even more, and with each thrust little
-spurts fly up from between my penis and her
+          <t>Her juices gush even more, and with each thrust
+little spurts fly up from between my penis and her
 pussy—spurt, spurt.</t>
         </is>
       </c>
@@ -30658,7 +30682,8 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan’s vagina was so warm and felt so good….</t>
+          <t>Rurichiyo-chan’s vagina was so warm and felt so
+good….</t>
         </is>
       </c>
       <c r="C1964" t="n">
@@ -30855,7 +30880,8 @@
       <c r="B1977" s="1" t="inlineStr">
         <is>
           <t>Every time I plunge in her pussy clenches tight, but
-with each smooth thrust the pleasure just won't stop…！</t>
+with each smooth thrust the pleasure just won't
+stop…！</t>
         </is>
       </c>
       <c r="C1977" t="n">
@@ -31726,8 +31752,8 @@
       </c>
       <c r="B2034" s="1" t="inlineStr">
         <is>
-          <t>「Hehe... from now on, let's have baby-making sex every
-day, okay？」</t>
+          <t>「Hehe... from now on, let's have baby-making sex
+every day, okay？」</t>
         </is>
       </c>
       <c r="C2034" t="n">
@@ -31940,8 +31966,8 @@
       </c>
       <c r="B2048" s="1" t="inlineStr">
         <is>
-          <t>...When morning comes, we immediately head back to the
-dorm.</t>
+          <t>...When morning comes, we immediately head back to
+the dorm.</t>
         </is>
       </c>
       <c r="C2048" t="n">
@@ -31972,8 +31998,8 @@
       </c>
       <c r="B2050" s="1" t="inlineStr">
         <is>
-          <t>It was only one day, but what if they're angry that we
-left them alone？</t>
+          <t>It was only one day, but what if they're angry that
+we left them alone？</t>
         </is>
       </c>
       <c r="C2050" t="n">
@@ -31988,8 +32014,8 @@
       </c>
       <c r="B2051" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I can't help but step into the entrance
-hesitantly.</t>
+          <t>Thinking that, I can't help but step into the
+entrance hesitantly.</t>
         </is>
       </c>
       <c r="C2051" t="n">
@@ -32262,8 +32288,8 @@
       </c>
       <c r="B2069" s="1" t="inlineStr">
         <is>
-          <t>「Because we thought you guys left because Miru and the
-others weren't getting along...」</t>
+          <t>「Because we thought you guys left because Miru and
+the others weren't getting along...」</t>
         </is>
       </c>
       <c r="C2069" t="n">
@@ -32399,8 +32425,8 @@
       </c>
       <c r="B2078" s="1" t="inlineStr">
         <is>
-          <t>「I'm sorry, I said it just to scare them a little, but
-I ended up getting anxious too...」</t>
+          <t>「I'm sorry, I said it just to scare them a little,
+but I ended up getting anxious too...」</t>
         </is>
       </c>
       <c r="C2078" t="n">
@@ -32753,7 +32779,8 @@
       </c>
       <c r="B2101" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's already getting a sense of being a mother.</t>
+          <t>Maybe she's already getting a sense of being a
+mother.</t>
         </is>
       </c>
       <c r="C2101" t="n">
@@ -32814,8 +32841,8 @@
       </c>
       <c r="B2105" s="1" t="inlineStr">
         <is>
-          <t>Seeing everyone doting on Rurichiyo-chan, I thought it
-over again.</t>
+          <t>Seeing everyone doting on Rurichiyo-chan, I thought
+it over again.</t>
         </is>
       </c>
       <c r="C2105" t="n">
@@ -32860,8 +32887,8 @@
       </c>
       <c r="B2108" s="1" t="inlineStr">
         <is>
-          <t>If that's the case, even if Rurichiyo-chan and I had a
-baby, there'd be nothing to worry about.</t>
+          <t>If that's the case, even if Rurichiyo-chan and I had
+a baby, there'd be nothing to worry about.</t>
         </is>
       </c>
       <c r="C2108" t="n">
@@ -32967,8 +32994,8 @@
       </c>
       <c r="B2115" s="1" t="inlineStr">
         <is>
-          <t>When our eyes met, we looked at each other and quietly
-smiled shyly...</t>
+          <t>When our eyes met, we looked at each other and
+quietly smiled shyly...</t>
         </is>
       </c>
       <c r="C2115" t="n">

--- a/processed_ruby_restored_xlsx/sc227_瑠璃９：かけおち.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc227_瑠璃９：かけおち.ss.xlsx
@@ -656,8 +656,8 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>I get a bit overexcited, which is my only flaw, but
-since it's what the teacher says, I'll feel down
+          <t>He gets a bit overexcited, which is his only flaw,
+but since it's what the teacher says, I'll feel down
 about it but I won't complain.</t>
         </is>
       </c>
@@ -688,8 +688,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>「Alright then... Janitor-sensei, do you have
-anything？」</t>
+          <t>Alright then... Janitor-sensei, do you have anything？</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1551,7 +1550,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>「Yes. Please take care of me.」</t>
+          <t>「Yes. Please take care of him.」</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1887,8 +1886,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>「Because Rin kept pretending to grab it over and
-over, geez！ Ugh！」</t>
+          <t>Because Rin kept pretending to grab it over and over,
+geez！ Ugh！</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1918,7 +1917,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>「But—it's not like we did anything like that…！」</t>
+          <t>But—it's not like we did anything like that…！</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2703,7 +2702,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>Hajime":"""</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2778,7 +2777,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>After seeing her back, I turned my gaze to Rin-chan.</t>
+          <t>After seeing their back, I turned my gaze to
+Rin-chan.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3506,7 +3506,7 @@
       <c r="B199" s="1" t="inlineStr">
         <is>
           <t>What on earth did it mean for someone like
-Rurichiyo-chan to have left the house...?</t>
+Rurichiyo-chan to have left the house...?"</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Whaaaat！? She actually said it！? To her sister！?</t>
+          <t>Whaaaat！? She actually said it！? To her sister！?"</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>By the time I finished all the preparations, three
+          <t>By the time he finished all the preparations, three
 hours had passed since leaving Rurichiyo-chan's room.</t>
         </is>
       </c>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, then sit over here~」</t>
+          <t>Yeah, then sit over here~</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>「Shall we do it one more time... okay, splash—！」</t>
+          <t>Shall we do it one more time... okay, splash—！</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -8007,8 +8007,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Suppressing another yawn that threatened to escape, I
-said, and Rurichiyo-chan sank down onto her knees
+          <t>Suppressing another yawn that threatened to escape,
+he said, and Rurichiyo-chan sank down onto her knees
 there.</t>
         </is>
       </c>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>As I say that, I lie down on my side and casually
+          <t>As he says that, I lie down on my side and casually
 position my penis out of sight.</t>
         </is>
       </c>
@@ -8454,7 +8454,7 @@
       <c r="B521" s="1" t="inlineStr">
         <is>
           <t>「When Oji-sama dodges things like that, it's usually
-when I'm thinking dirty thoughts...！」</t>
+when he's thinking dirty thoughts...！」</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B558" s="1" t="inlineStr">
         <is>
-          <t>...I spoke without thinking and laughed without a
+          <t>...He spoke without thinking and laughed without a
 care.</t>
         </is>
       </c>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>「Nnfff...！ Nn, nnn！ Nn~...！」</t>
+          <t>Nnfff...！ Nn, nnn！ Nn~...！</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10076,7 +10076,7 @@
       <c r="B627" s="1" t="inlineStr">
         <is>
           <t>I think it’s milder than sucking, but it still looks
-like she’s getting turned on enough.</t>
+like they’re getting turned on enough.</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -10196,8 +10196,8 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaa... ah！ Ah, aah...！ Ya...！ Yaa... desu yoo...
-nn, nn！」</t>
+          <t>Fuwaa... ah！ Ah, aah...！ Ya...！ Yaa... desu yoo...
+nn, nn！</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -10350,8 +10350,8 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>「Nn...ahh, uncle...sir...！ But... I still can't...
-not here... nnn！」</t>
+          <t>Nn...ahh, uncle...sir...！ But... I still can't... not
+here... nnn！</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnng~！ Nfuu, fuuuh...！」</t>
+          <t>Nn！ Nnng~！ Nfuu, fuuuh...！</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="B677" s="1" t="inlineStr">
         <is>
-          <t>「Nn... chu, chuu...！」</t>
+          <t>Nn... chu, chuu...！</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -10907,8 +10907,8 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>「Mm？ If it’s my voice you mean, I’ve been making one
-for a while now, you know？」</t>
+          <t>Mm？ If it’s my voice you mean, I’ve been making one
+for a while now, you know？</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -11014,8 +11014,8 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！ Nfu！ Fuh, uu！ Faa... ah, aaah... ah~... ah！
-Aaaah...」</t>
+          <t>Nn...！ Nfu！ Fuh, uu！ Faa... ah, aaah... ah~... ah！
+Aaaah...</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -11105,8 +11105,8 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Haa... yes, yes...！ It feels good... it feels so
-good... fuwaaa...！」</t>
+          <t>Ah！ Haa... yes, yes...！ It feels good... it feels so
+good... fuwaaa...！</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11198,8 +11198,8 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>「Ha... haai... fuwaa, ah, aa... Oji-sama...
-Oji-samaaa...！」</t>
+          <t>Ha... haai... fuwaa, ah, aa... Oji-sama...
+Oji-samaaa...！</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -11214,8 +11214,8 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>Now that she’s stopped holding back so strangely, her
-voice has softened too.</t>
+          <t>Now that they’ve stopped holding back so strangely,
+their voice has softened too.</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>When I let her taste my sexual fluids, I can see a
+          <t>When I let them taste my sexual fluids, I can see a
 face blushing with shame like nothing else.</t>
         </is>
       </c>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>「Hiuu！？ Ah, ah, ah, aahhhh...！」</t>
+          <t>Hiuu！？ Ah, ah, ah, aahhhh...！</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>「Nngu, u... dyu, dyu-dyuu...！」</t>
+          <t>Nngu, u... dyu, dyu-dyuu...！</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -12938,8 +12938,7 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>「Uwa... ah...! Th-that's... no... Oji-sama! Kuu...
-n!」</t>
+          <t>Uwa... ah...! Th-that's... no... Oji-sama! Kuu... n!</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13000,7 +12999,7 @@
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>「Nngu, ngngngu... dyuu-dyu！」</t>
+          <t>Nngu, ngngngu... dyuu-dyu！</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -13337,7 +13336,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13446,7 +13445,7 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -13539,7 +13538,7 @@
       </c>
       <c r="B852" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -13646,7 +13645,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13784,8 +13783,8 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>When I make Rurichiyo-chan get on all fours, I can’t
-resist anymore and press my penis against her.</t>
+          <t>When Rurichiyo-chan is made to get on all fours, she
+can't help it and presses her penis against (it).</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -13893,7 +13892,7 @@
       </c>
       <c r="B875" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I kinda feel like toying with me a
+          <t>Thinking that, I kinda feel like toying with him a
 little.</t>
         </is>
       </c>
@@ -13971,8 +13970,9 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>I press the tip of my penis against the soft flesh
-and squeeze it, but still doesn't try to put it in.</t>
+          <t>He presses the tip of his penis against the soft
+flesh and squeezes it, but still doesn't try to put
+it in.</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -14620,8 +14620,8 @@
       </c>
       <c r="B922" s="1" t="inlineStr">
         <is>
-          <t>「Haa... ah, aa... ya, Oji-sama... Oji-samaa... pff,
-fuuuh, nnff！ fu, fu...！」</t>
+          <t>Haa... ah, aa... ya, Oji-sama... Oji-samaa... pff,
+fuuuh, nnff！ fu, fu...！</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -14713,9 +14713,8 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Y-yes. It feels better when you go all the
-way deep into my stomach... nngh！ I-I'm feeling
-it...！」</t>
+          <t>Mmm... Y-yes. It feels better when you go all the way
+deep into my stomach... nngh！ I-I'm feeling it...！</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -14824,7 +14823,7 @@
       <c r="B935" s="1" t="inlineStr">
         <is>
           <t>Then, a gush of wetness spills out from deep in the
-vagina, hotly soaking the tip of my penis….</t>
+vagina, hotly soaking the tip of his penis….</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -15238,8 +15237,8 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>And wetness leaks again from her womb, steadily
-making the inside of her vagina grow hot...</t>
+          <t>And wetness leaks again from my womb, steadily making
+the inside of my vagina grow hot...</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -16037,7 +16036,7 @@
       <c r="B1014" s="1" t="inlineStr">
         <is>
           <t>I let out a soft, needy little sound and sway my hips
-to tease her.</t>
+to tease them.</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -16574,7 +16573,7 @@
       </c>
       <c r="B1049" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn-ah！ Ah… y-yeah… the usual… nn！ Nn, nnn~…！」</t>
+          <t>Nn！ Nn-ah！ Ah… y-yeah… the usual… nn！ Nn, nnn~…！</t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -17187,7 +17186,7 @@
       </c>
       <c r="B1089" s="1" t="inlineStr">
         <is>
-          <t>「Nn~！ Nn~！ Hf！ Huu…！ Ah, aa…！ Aah！ Aah~…！」</t>
+          <t>Nn~！ Nn~！ Hf！ Huu…！ Ah, aa…！ Aah！ Aah~…！</t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -17265,8 +17264,8 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>「Fuwa！ Ah... ah！ Oji-sama！ Ah！ That... it's going to
-make me lose it... ugh！」</t>
+          <t>Fuwa！ Ah... ah！ Oji-sama！ Ah！ That... it's going to
+make me lose it... ugh！</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -17281,8 +17280,8 @@
       </c>
       <c r="B1095" s="1" t="inlineStr">
         <is>
-          <t>Once I really started moving my hips, Rurichiyo-chan
-got worked up in no time.</t>
+          <t>Once he really started moving his hips,
+Rurichiyo-chan got worked up in no time.</t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -17344,7 +17343,7 @@
       </c>
       <c r="B1099" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -17468,7 +17467,7 @@
       </c>
       <c r="B1107" s="1" t="inlineStr">
         <is>
-          <t>I felt Rurichiyo-chan and picked up the pace.</t>
+          <t>He felt Rurichiyo-chan and picked up the pace.</t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -17696,7 +17695,7 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>「Nn-ah！？　Aaaaaahhhhhh—！」</t>
+          <t>Nn-ah！？　Aaaaaahhhhhh—！</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17727,7 +17726,7 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>Her vaginal walls undulate, driving my penis to
+          <t>Her vaginal walls undulate, driving his penis to
 climax.</t>
         </is>
       </c>
@@ -17912,8 +17911,8 @@
       </c>
       <c r="B1136" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah！ Ah！ Aah！ Aahhh！ Yah... yah！ Kuh！ Hah！ Hah！
-Hah！ Hah！」</t>
+          <t>Fwaaah！ Ah！ Aah！ Aahhh！ Yah... yah！ Kuh！ Hah！ Hah！
+Hah！ Hah！</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -18175,7 +18174,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>The throbbing of my penis and the tightening of her
+          <t>The throbbing of his penis and the tightening of her
 pussy were perfectly in sync, to the point I felt
 like even our mucous membranes had become one.</t>
         </is>
@@ -18652,7 +18651,7 @@
       </c>
       <c r="B1184" s="1" t="inlineStr">
         <is>
-          <t>「Nng！ Fuwaaa...！ Aaah！ Aaah！ Aah... fuku—！ Uuuu...！」</t>
+          <t>Nng！ Fuwaaa...！ Aaah！ Aaah！ Aah... fuku—！ Uuuu...！</t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -18714,7 +18713,7 @@
       </c>
       <c r="B1188" s="1" t="inlineStr">
         <is>
-          <t>「Nn！　Nnnh！　Nnnh！　Huh！　Fwaaah！　Aah！　Fuu...！」</t>
+          <t>Nn！　Nnnh！　Nnnh！　Huh！　Fwaaah！　Aah！　Fuu...！</t>
         </is>
       </c>
       <c r="C1188" t="n">
@@ -18884,7 +18883,7 @@
       </c>
       <c r="B1199" s="1" t="inlineStr">
         <is>
-          <t>「Fuyaaa!？ Ah! Ahh! Hot...! Nn! Huuu! Huu...!」</t>
+          <t>Fuyaaa!？ Ah! Ahh! Hot...! Nn! Huuu! Huu...!</t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -19865,7 +19864,7 @@
       </c>
       <c r="B1263" s="1" t="inlineStr">
         <is>
-          <t>She probably just thinks I'm simply washing my body.</t>
+          <t>They probably just think I'm simply washing my body.</t>
         </is>
       </c>
       <c r="C1263" t="n">
@@ -20033,7 +20032,7 @@
       </c>
       <c r="B1274" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1274" t="n">
@@ -20048,7 +20047,7 @@
       </c>
       <c r="B1275" s="1" t="inlineStr">
         <is>
-          <t>「Kyaa...！　Oji-sama~？」</t>
+          <t>Kyaa...！　Oji-sama~？</t>
         </is>
       </c>
       <c r="C1275" t="n">
@@ -20078,7 +20077,7 @@
       </c>
       <c r="B1277" s="1" t="inlineStr">
         <is>
-          <t>「Ah, you've got to wash the front properly too...！」</t>
+          <t>Ah, you」ve got to wash the front properly too...！</t>
         </is>
       </c>
       <c r="C1277" t="n">
@@ -20093,7 +20092,7 @@
       </c>
       <c r="B1278" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1278" t="n">
@@ -20108,8 +20107,8 @@
       </c>
       <c r="B1279" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnh！ Please tell me before you do that... nn,
-n—！」</t>
+          <t>Nn... nnh！ Please tell me before you do that... nn,
+n—！</t>
         </is>
       </c>
       <c r="C1279" t="n">
@@ -20171,7 +20170,7 @@
       </c>
       <c r="B1283" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -20186,7 +20185,7 @@
       </c>
       <c r="B1284" s="1" t="inlineStr">
         <is>
-          <t>「Hyaaan！ I'll wash there myself...！」</t>
+          <t>Hyaaan！ I」ll wash there myself...！</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -20216,7 +20215,7 @@
       </c>
       <c r="B1286" s="1" t="inlineStr">
         <is>
-          <t>「It’s fine, it’s fine. Don’t hold back...」</t>
+          <t>It’s fine, it’s fine. Don’t hold back...</t>
         </is>
       </c>
       <c r="C1286" t="n">
@@ -20263,8 +20262,8 @@
       </c>
       <c r="B1289" s="1" t="inlineStr">
         <is>
-          <t>「I messed it up with mine, so I'll make it all nice
-and clean for you...！」</t>
+          <t>I messed it up with mine, so I」ll make it all nice
+and clean for you...！</t>
         </is>
       </c>
       <c r="C1289" t="n">
@@ -20279,7 +20278,7 @@
       </c>
       <c r="B1290" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1290" t="n">
@@ -20294,7 +20293,7 @@
       </c>
       <c r="B1291" s="1" t="inlineStr">
         <is>
-          <t>「Nfuu... nn！ Jeez, jeez...！」</t>
+          <t>Nfuu... nn！ Jeez, jeez...！</t>
         </is>
       </c>
       <c r="C1291" t="n">
@@ -20355,7 +20354,7 @@
       </c>
       <c r="B1295" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1295" t="n">
@@ -20370,8 +20369,8 @@
       </c>
       <c r="B1296" s="1" t="inlineStr">
         <is>
-          <t>「Ah... then I suppose I’ll have to wash Oji-sama’s
-penis properly too, won’t I？」</t>
+          <t>Ah... then I suppose I’ll have to wash Oji-sama’s
+penis properly too, won’t I？</t>
         </is>
       </c>
       <c r="C1296" t="n">
@@ -20401,7 +20400,7 @@
       </c>
       <c r="B1298" s="1" t="inlineStr">
         <is>
-          <t>「Eh...？　Ooooh...」</t>
+          <t>Eh...？　Ooooh...</t>
         </is>
       </c>
       <c r="C1298" t="n">
@@ -20416,7 +20415,7 @@
       </c>
       <c r="B1299" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan reaches back, searching for my penis
+          <t>Rurichiyo-chan reaches back, searching for his penis
 with her hand.</t>
         </is>
       </c>
@@ -20448,7 +20447,7 @@
       </c>
       <c r="B1301" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1301" t="n">
@@ -21496,7 +21495,7 @@
       </c>
       <c r="B1369" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo</t>
+          <t>Kikuchiyo-baa-chan</t>
         </is>
       </c>
       <c r="C1369" t="n">
@@ -21511,8 +21510,8 @@
       </c>
       <c r="B1370" s="1" t="inlineStr">
         <is>
-          <t>「Hajime... you too！ Doing something so careless and
-slack...！」</t>
+          <t>Hajime... you too！ Doing something so careless and
+slack...！</t>
         </is>
       </c>
       <c r="C1370" t="n">
@@ -21543,7 +21542,7 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo</t>
+          <t>Kikuchiyo-baa-chan</t>
         </is>
       </c>
       <c r="C1372" t="n">
@@ -21558,8 +21557,8 @@
       </c>
       <c r="B1373" s="1" t="inlineStr">
         <is>
-          <t>「Anyway, a worthless fellow like you running off in
-an elopement — it's a hundred years too soon...！」</t>
+          <t>Anyway, a worthless fellow like you running off in an
+elopement — it's a hundred years too soon...！</t>
         </is>
       </c>
       <c r="C1373" t="n">
@@ -21653,7 +21652,7 @@
       </c>
       <c r="B1379" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo</t>
+          <t>Kikuchiyo-baa-chan</t>
         </is>
       </c>
       <c r="C1379" t="n">
@@ -21668,8 +21667,8 @@
       </c>
       <c r="B1380" s="1" t="inlineStr">
         <is>
-          <t>「Good grief... more importantly, what do you mean
-leaving the dorm kids behind like that？」</t>
+          <t>Good grief... more importantly, what do you mean
+leaving the dorm kids behind like that？</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -21699,7 +21698,7 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>「That... I'm sorry.」</t>
+          <t>That... I'm sorry.</t>
         </is>
       </c>
       <c r="C1382" t="n">
@@ -21761,7 +21760,7 @@
       </c>
       <c r="B1386" s="1" t="inlineStr">
         <is>
-          <t>「Th-that was because I insisted！」</t>
+          <t>Th-that was because I insisted！</t>
         </is>
       </c>
       <c r="C1386" t="n">
@@ -21776,7 +21775,7 @@
       </c>
       <c r="B1387" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo</t>
+          <t>Kikuchiyo-baa-chan</t>
         </is>
       </c>
       <c r="C1387" t="n">
@@ -21791,8 +21790,8 @@
       </c>
       <c r="B1388" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo... just because you begged doesn't make
-you Hajime's get-out-of-jail card, you know？」</t>
+          <t>Rurichiyo... just because you begged doesn't make you
+Hajime's get-out-of-jail card, you know？</t>
         </is>
       </c>
       <c r="C1388" t="n">
@@ -21853,7 +21852,7 @@
       </c>
       <c r="B1392" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo</t>
+          <t>Kikuchiyo-baa-chan</t>
         </is>
       </c>
       <c r="C1392" t="n">
@@ -21868,9 +21867,9 @@
       </c>
       <c r="B1393" s="1" t="inlineStr">
         <is>
-          <t>「Absolutely outrageous...！ And on top of it all, you
+          <t>Absolutely outrageous...！ And on top of it all, you
 go cavorting in the hot springs with my Rurichiyo —
-I'm jealous...！」</t>
+I'm jealous...！</t>
         </is>
       </c>
       <c r="C1393" t="n">
@@ -21945,7 +21944,7 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>「Ughhh—？」</t>
+          <t>Ughhh—？</t>
         </is>
       </c>
       <c r="C1398" t="n">
@@ -22251,7 +22250,7 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>「Um... Great-great-grandmother？」</t>
+          <t>Um... Great-great-grandmother？</t>
         </is>
       </c>
       <c r="C1418" t="n">
@@ -23816,8 +23815,8 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>「Well... it took me a while too to make things add up
-inside myself...」</t>
+          <t>Well... it took me a while too to make things add up
+inside myself...</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -24500,7 +24499,7 @@
       </c>
       <c r="B1563" s="1" t="inlineStr">
         <is>
-          <t>「Ah…！  ………」</t>
+          <t>Ah…！  ………</t>
         </is>
       </c>
       <c r="C1563" t="n">
@@ -25033,7 +25032,7 @@
       </c>
       <c r="B1598" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1598" t="n">
@@ -25113,7 +25112,7 @@
       </c>
       <c r="B1603" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1603" t="n">
@@ -25189,7 +25188,7 @@
       </c>
       <c r="B1608" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1608" t="n">
@@ -25297,7 +25296,7 @@
       </c>
       <c r="B1615" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C1615" t="n">
@@ -26173,8 +26172,8 @@
       </c>
       <c r="B1672" s="1" t="inlineStr">
         <is>
-          <t>「Fah, faaah...！  Y-yes... it feels so good... nn！
-Muuuh！」</t>
+          <t>Fah, faaah...！  Y-yes... it feels so good... nn！
+Muuuh！</t>
         </is>
       </c>
       <c r="C1672" t="n">
@@ -27545,7 +27544,7 @@
       </c>
       <c r="B1761" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn！ Nn！ Ah... ya, haa...！ Ah！ Ah！ Ah！ Ah！ Ah！」</t>
+          <t>Nn！ Nn！ Nn！ Ah... ya, haa...！ Ah！ Ah！ Ah！ Ah！ Ah！</t>
         </is>
       </c>
       <c r="C1761" t="n">
@@ -27730,7 +27729,7 @@
       </c>
       <c r="B1773" s="1" t="inlineStr">
         <is>
-          <t>「Nn-ah！　Aaaaahh！　Aaaaahhh！」</t>
+          <t>Nn-ah！　Aaaaahh！　Aaaaahhh！</t>
         </is>
       </c>
       <c r="C1773" t="n">
@@ -27777,7 +27776,7 @@
       </c>
       <c r="B1776" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnnh...！」</t>
+          <t>Nn... nnnh...！</t>
         </is>
       </c>
       <c r="C1776" t="n">
@@ -27822,7 +27821,7 @@
       </c>
       <c r="B1779" s="1" t="inlineStr">
         <is>
-          <t>「Nnfu...！　Nn！　Nnnnnn~~！」</t>
+          <t>Nnfu...！　Nn！　Nnnnnn~~！</t>
         </is>
       </c>
       <c r="C1779" t="n">
@@ -27884,8 +27883,8 @@
       </c>
       <c r="B1783" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh...! Hah! Ahh... there it is... cum, so much...
-hehe...!」</t>
+          <t>Aahhh...! Hah! Ahh... there it is... cum, so much...
+hehe...!</t>
         </is>
       </c>
       <c r="C1783" t="n">
@@ -28546,7 +28545,7 @@
       </c>
       <c r="B1826" s="1" t="inlineStr">
         <is>
-          <t>Pushing my penis in and pressing the tip against the
+          <t>Pushing his penis in and pressing the tip against the
 opening of her uterus, Rurichiyo-chan melted into a
 rapturous, moaning expression.</t>
         </is>
@@ -28687,8 +28686,8 @@
       </c>
       <c r="B1835" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnnu...！ I— I too... I too！ I love you... ah,
-fuaaah！」</t>
+          <t>Nn！ Nnnu...！ I— I too... I too！ I love you... ah,
+fuaaah！</t>
         </is>
       </c>
       <c r="C1835" t="n">
@@ -28833,7 +28832,7 @@
       </c>
       <c r="B1844" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C1844" t="n">
@@ -29663,9 +29662,9 @@
       </c>
       <c r="B1898" s="1" t="inlineStr">
         <is>
-          <t>On top of that, her cheeks were flushed a faint rosy
-red, and the yukata was all rumpled from being so
-thoroughly messed up….</t>
+          <t>On top of that, their cheeks were flushed a faint
+rosy red, and the yukata was all rumpled from being
+so thoroughly messed up….</t>
         </is>
       </c>
       <c r="C1898" t="n">
@@ -29725,7 +29724,7 @@
       </c>
       <c r="B1902" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！ Hah, y-yes...！」</t>
+          <t>Ah...！ Hah, y-yes...！</t>
         </is>
       </c>
       <c r="C1902" t="n">
@@ -30434,7 +30433,7 @@
       <c r="B1948" s="1" t="inlineStr">
         <is>
           <t>Her juices gush even more, and with each thrust
-little spurts fly up from between my penis and her
+little spurts fly up from between his penis and her
 pussy—spurt, spurt.</t>
         </is>
       </c>
@@ -30465,7 +30464,7 @@
       </c>
       <c r="B1950" s="1" t="inlineStr">
         <is>
-          <t>「Fwuaaah！ Fwi！ Fwi！ Fuuuh…！ Huh！ Huh！ Fwaa… Ah！ Ah！」</t>
+          <t>Fwuaaah！ Fwi！ Fwi！ Fuuuh…！ Huh！ Huh！ Fwaa… Ah！ Ah！</t>
         </is>
       </c>
       <c r="C1950" t="n">
@@ -30557,8 +30556,8 @@
       </c>
       <c r="B1956" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaah！ Ah！ Aah！ Wahf！ Unn... nngh, n！ Fah！
-Fwaaaah...！」</t>
+          <t>Fuwaaah！ Ah！ Aah！ Wahf！ Unn... nngh, n！ Fah！
+Fwaaaah...！</t>
         </is>
       </c>
       <c r="C1956" t="n">
@@ -30758,7 +30757,7 @@
       </c>
       <c r="B1969" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaay！ Yes！ I'm gonna have a baby！」</t>
+          <t>Fuwaaay！ Yes！ I'm gonna have a baby！</t>
         </is>
       </c>
       <c r="C1969" t="n">
@@ -30879,8 +30878,8 @@
       </c>
       <c r="B1977" s="1" t="inlineStr">
         <is>
-          <t>Every time I plunge in her pussy clenches tight, but
-with each smooth thrust the pleasure just won't
+          <t>Every time he plunges in her pussy clenches tight,
+but with each smooth thrust the pleasure just won't
 stop…！</t>
         </is>
       </c>
@@ -31079,7 +31078,7 @@
       </c>
       <c r="B1990" s="1" t="inlineStr">
         <is>
-          <t>「Ahyahaaaaaahhh...！ Ah... ahh！ Aahhhhhhh！」</t>
+          <t>Ahyahaaaaaahhh...！ Ah... ahh！ Aahhhhhhh！</t>
         </is>
       </c>
       <c r="C1990" t="n">
@@ -31109,7 +31108,7 @@
       </c>
       <c r="B1992" s="1" t="inlineStr">
         <is>
-          <t>Injecting my semen with the intent to fertilize her,
+          <t>Injecting his semen with the intent to fertilize her,
 Rurichiyo-chan was likewise swept away by a huge wave
 of climax.</t>
         </is>
@@ -31186,8 +31185,8 @@
       </c>
       <c r="B1997" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah... Afuaaahh... Ah, aaahh... Ah！
-Aaaahhhhaaahh...！」</t>
+          <t>Fwaaah... Afuaaahh... Ah, aaahh... Ah！
+Aaaahhhhaaahh...！</t>
         </is>
       </c>
       <c r="C1997" t="n">
@@ -31218,7 +31217,7 @@
       <c r="B1999" s="1" t="inlineStr">
         <is>
           <t>My climax and Rurichiyo-chan's climax overlap, and
-semen is squeezed out of her pussy…！</t>
+semen is squeezed out of my pussy…！</t>
         </is>
       </c>
       <c r="C1999" t="n">
@@ -31369,7 +31368,7 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>「…uh…uh…？」</t>
+          <t>…uh…uh…？</t>
         </is>
       </c>
       <c r="C2009" t="n">
@@ -31720,7 +31719,7 @@
       </c>
       <c r="B2032" s="1" t="inlineStr">
         <is>
-          <t>We had serious sex to make a baby and I finished
+          <t>We had serious sex to make a baby and he finished
 inside me, but I still want to keep feeling like
 lovers.</t>
         </is>
@@ -32505,7 +32504,7 @@
       <c r="B2083" s="1" t="inlineStr">
         <is>
           <t>And so everyone just kept getting more and more
-worried...？</t>
+worried...？"</t>
         </is>
       </c>
       <c r="C2083" t="n">
